--- a/uploads/Employee Reports.xlsx
+++ b/uploads/Employee Reports.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\trainingcoverage\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\trainingcoverageREV\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B1361B-E049-4E05-B18D-AA3F5EA9CB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B0F75F-5158-4219-ACEC-55D005989B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A4D7503A-3666-4DDD-8602-29F3BCAE2D90}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Lembar1!$A$1:$J$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -902,6 +905,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BDF1F9-1293-404E-B1E8-921D56B9FBE2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -912,7 +918,7 @@
     <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -1132,6 +1138,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>